--- a/data/trans_camb/P43C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Habitat-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,39</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,39</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5,75</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,13; 20,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,74; 14,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,87; 11,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 20,58</t>
+          <t>10,13; 20,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 13,56</t>
+          <t>3,74; 14,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,9</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,69; 20,58</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,92; 13,56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,61; 10,9</t>
+          <t>0,87; 11,4</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12,2%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,53; 47,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,55; 31,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,75; 25,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,92; 46,68</t>
+          <t>20,53; 47,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 30,79</t>
+          <t>7,55; 31,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 24,72</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,92; 46,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5,8; 30,79</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 24,72</t>
+          <t>1,75; 25,92</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>13,32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,47</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,43; 17,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,07; 18,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,15; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 17,38</t>
+          <t>8,43; 17,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 17,87</t>
+          <t>9,07; 18,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,69</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>8,31; 17,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,24; 17,87</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 4,69</t>
+          <t>-4,15; 4,94</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,79; 35,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,63; 37,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,68; 9,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,23; 35,45</t>
+          <t>15,79; 35,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 36,64</t>
+          <t>16,63; 37,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 9,54</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,23; 35,45</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17,01; 36,64</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-7,91; 9,54</t>
+          <t>-7,68; 9,85</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,33</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-7,75</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,7</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8,33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>-7,75</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,74; 18,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,29; 13,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-34,24; 13,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,59</t>
+          <t>8,74; 18,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 13,02</t>
+          <t>3,29; 13,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-36,99; 12,91</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,44; 18,59</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2,6; 13,02</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-36,99; 12,91</t>
+          <t>-34,24; 13,78</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-13,69%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-13,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>-13,69%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,53; 35,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,42; 24,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-58,7; 24,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,57; 34,92</t>
+          <t>14,53; 35,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,41; 23,94</t>
+          <t>5,42; 24,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 23,11</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>14,57; 34,92</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4,41; 23,94</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-63,55; 23,11</t>
+          <t>-58,7; 24,63</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9,05</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>8,8</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,86; 9,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,88; 13,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,43; 17,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,52</t>
+          <t>0,86; 9,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,33</t>
+          <t>4,88; 13,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 16,49</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 9,52</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5,09; 13,33</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3,81; 16,49</t>
+          <t>3,43; 17,21</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>15,11%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,57; 17,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,0; 24,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,75; 30,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 17,04</t>
+          <t>1,57; 17,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,5; 23,92</t>
+          <t>8,0; 24,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 28,81</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,63; 17,04</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8,5; 23,92</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6,31; 28,81</t>
+          <t>5,75; 30,52</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,29</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,13</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2,16</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,63</t>
+          <t>8,89; 13,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,95; 12,56</t>
+          <t>7,82; 12,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 7,85</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 13,63</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>7,95; 12,56</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; 7,85</t>
+          <t>-12,99; 7,8</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,97%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,13; 26,12</t>
+          <t>16,14; 25,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,75</t>
+          <t>14,23; 23,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 14,66</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>16,13; 26,12</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 23,75</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>-18,72; 14,66</t>
+          <t>-23,65; 14,55</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1371,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>

--- a/data/trans_camb/P43C-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43C-Habitat-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>4,94</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 20,76</t>
+          <t>10,25; 20,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 14,03</t>
+          <t>3,35; 14,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,4</t>
+          <t>-0,63; 9,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 20,76</t>
+          <t>10,25; 20,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,74; 14,03</t>
+          <t>3,35; 14,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,4</t>
+          <t>-0,63; 9,77</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 47,44</t>
+          <t>21,37; 47,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 31,76</t>
+          <t>7,1; 31,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 25,92</t>
+          <t>-1,0; 22,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 47,44</t>
+          <t>21,37; 47,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 31,76</t>
+          <t>7,1; 31,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 25,92</t>
+          <t>-1,0; 22,36</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,48</t>
+          <t>8,38; 17,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 18,15</t>
+          <t>8,72; 17,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,94</t>
+          <t>-4,27; 4,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,48</t>
+          <t>8,38; 17,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 18,15</t>
+          <t>8,72; 17,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 4,94</t>
+          <t>-4,27; 4,62</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 35,72</t>
+          <t>15,21; 34,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 37,17</t>
+          <t>16,24; 35,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 9,85</t>
+          <t>-7,88; 9,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 35,72</t>
+          <t>15,21; 34,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 37,17</t>
+          <t>16,24; 35,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 9,85</t>
+          <t>-7,88; 9,31</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>8,71</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 18,88</t>
+          <t>8,26; 18,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 13,0</t>
+          <t>3,3; 13,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 13,78</t>
+          <t>2,93; 14,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 18,88</t>
+          <t>8,26; 18,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 13,0</t>
+          <t>3,3; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 13,78</t>
+          <t>2,93; 14,02</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,69%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,53; 35,24</t>
+          <t>13,99; 34,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,32</t>
+          <t>5,49; 25,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 24,63</t>
+          <t>5,0; 26,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,53; 35,24</t>
+          <t>13,99; 34,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,32</t>
+          <t>5,49; 25,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 24,63</t>
+          <t>5,0; 26,09</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>4,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>4,18</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,66</t>
+          <t>1,32; 10,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,85</t>
+          <t>5,0; 13,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,21</t>
+          <t>-0,39; 8,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,66</t>
+          <t>1,32; 10,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,88; 13,85</t>
+          <t>5,0; 13,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,21</t>
+          <t>-0,39; 8,51</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 17,4</t>
+          <t>2,2; 18,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 24,89</t>
+          <t>8,23; 25,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 30,52</t>
+          <t>-0,59; 15,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 17,4</t>
+          <t>2,2; 18,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 24,89</t>
+          <t>8,23; 25,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 30,52</t>
+          <t>-0,59; 15,14</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,51</t>
+          <t>8,68; 13,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,42</t>
+          <t>7,75; 12,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 7,8</t>
+          <t>1,49; 6,45</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1334,32 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,14; 25,63</t>
+          <t>15,8; 25,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,23; 23,63</t>
+          <t>14,21; 24,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 14,55</t>
+          <t>2,77; 12,26</t>
         </is>
       </c>
     </row>
